--- a/InputData/trans/MPoEFUbVT/Max Perc of Each Fuel Usable by Veh Tech.xlsx
+++ b/InputData/trans/MPoEFUbVT/Max Perc of Each Fuel Usable by Veh Tech.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10711"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/users/nathaniyer/library/containers/com.microsoft.excel/data/state-eps-data-repository/template_state/trans/mpoefubvt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zsubin/Documents/Code/eps-newmexico/InputData/trans/MPoEFUbVT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3609C5-30CF-1E4D-A1D3-ADCD6C28CEBD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FF5151-DF1A-5942-8C9B-3772572E4B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="460" windowWidth="23960" windowHeight="12100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2260" yWindow="2240" windowWidth="32940" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -6899,143 +6899,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -11228,7 +11228,7 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -11249,10 +11249,10 @@
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.2">
@@ -11385,123 +11385,123 @@
       </c>
       <c r="F11">
         <f>TREND($A$7:$B$7,$A$6:$B$6,F10)</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G11">
         <f t="shared" ref="G11:AI11" si="0">TREND($A$7:$B$7,$A$6:$B$6,G10)</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J11">
         <f t="shared" si="0"/>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <f t="shared" si="0"/>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L11">
         <f t="shared" si="0"/>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N11">
         <f t="shared" si="0"/>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O11">
         <f t="shared" si="0"/>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P11">
         <f t="shared" si="0"/>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q11">
         <f t="shared" si="0"/>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R11">
         <f t="shared" si="0"/>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S11">
         <f t="shared" si="0"/>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T11">
         <f t="shared" si="0"/>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U11">
         <f t="shared" si="0"/>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V11">
         <f t="shared" si="0"/>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W11">
         <f t="shared" si="0"/>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X11">
         <f t="shared" si="0"/>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y11">
         <f t="shared" si="0"/>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA11">
         <f t="shared" si="0"/>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB11">
         <f t="shared" si="0"/>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC11">
         <f t="shared" si="0"/>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD11">
         <f t="shared" si="0"/>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE11">
         <f t="shared" si="0"/>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF11">
         <f t="shared" si="0"/>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG11">
         <f t="shared" si="0"/>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH11">
         <f t="shared" si="0"/>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI11">
         <f t="shared" si="0"/>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.2">
@@ -15910,143 +15910,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -17171,143 +17171,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -24621,143 +24621,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -25882,143 +25882,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -31884,123 +31884,123 @@
       </c>
       <c r="F6">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G6">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H6">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I6">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J6">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L6">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M6">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N6">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O6">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P6">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q6">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R6">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S6">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T6">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U6">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V6">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W6">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X6">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y6">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z6">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA6">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB6">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC6">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD6">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE6">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF6">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG6">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH6">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI6">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -33218,123 +33218,123 @@
       </c>
       <c r="F7">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G7">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H7">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I7">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J7">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L7">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M7">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N7">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O7">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P7">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q7">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R7">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S7">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T7">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U7">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V7">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W7">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X7">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y7">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z7">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA7">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB7">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC7">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD7">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE7">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF7">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG7">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH7">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI7">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -39155,123 +39155,123 @@
       </c>
       <c r="F6">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G6">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H6">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I6">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J6">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L6">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M6">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N6">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O6">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P6">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q6">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R6">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S6">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T6">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U6">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V6">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W6">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X6">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y6">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z6">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA6">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB6">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC6">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD6">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE6">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF6">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG6">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH6">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI6">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -40489,123 +40489,123 @@
       </c>
       <c r="F7">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G7">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H7">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I7">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J7">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L7">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M7">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N7">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O7">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P7">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q7">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R7">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S7">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T7">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U7">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V7">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W7">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X7">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y7">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z7">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA7">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB7">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC7">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD7">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE7">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF7">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG7">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH7">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI7">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -46426,123 +46426,123 @@
       </c>
       <c r="F6">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G6">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H6">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I6">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J6">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L6">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M6">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N6">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O6">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P6">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q6">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R6">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S6">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T6">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U6">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V6">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W6">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X6">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y6">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z6">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA6">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB6">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC6">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD6">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE6">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF6">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG6">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH6">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI6">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -47760,123 +47760,123 @@
       </c>
       <c r="F7">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G7">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H7">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I7">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J7">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L7">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M7">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N7">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O7">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P7">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q7">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R7">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S7">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T7">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U7">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V7">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W7">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X7">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y7">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z7">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA7">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB7">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC7">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD7">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE7">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF7">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG7">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH7">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI7">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -52471,123 +52471,123 @@
       </c>
       <c r="F6">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G6">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H6">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I6">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J6">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L6">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M6">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N6">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O6">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P6">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q6">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R6">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S6">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T6">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U6">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V6">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W6">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X6">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y6">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z6">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA6">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB6">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC6">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD6">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE6">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF6">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG6">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH6">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI6">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -53805,123 +53805,123 @@
       </c>
       <c r="F7">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G7">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H7">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I7">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J7">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L7">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M7">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N7">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O7">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P7">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q7">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R7">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S7">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T7">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U7">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V7">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W7">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X7">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y7">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z7">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA7">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB7">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC7">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD7">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE7">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF7">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG7">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH7">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI7">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -59777,123 +59777,123 @@
       </c>
       <c r="F6">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G6">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H6">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I6">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J6">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L6">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M6">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N6">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O6">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P6">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q6">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R6">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S6">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T6">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U6">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V6">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W6">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X6">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y6">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z6">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA6">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB6">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC6">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD6">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE6">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF6">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG6">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH6">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI6">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -61111,123 +61111,123 @@
       </c>
       <c r="F7">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G7">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H7">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I7">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J7">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L7">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M7">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N7">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O7">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P7">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q7">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R7">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S7">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T7">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U7">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V7">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W7">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X7">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y7">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z7">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA7">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB7">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC7">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD7">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE7">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF7">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG7">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH7">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI7">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -65822,123 +65822,123 @@
       </c>
       <c r="F6">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G6">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H6">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I6">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J6">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L6">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M6">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N6">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O6">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P6">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q6">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R6">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S6">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T6">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U6">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V6">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W6">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X6">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y6">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z6">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA6">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB6">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC6">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD6">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE6">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF6">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG6">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH6">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI6">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.2">
@@ -67156,123 +67156,123 @@
       </c>
       <c r="F7">
         <f>'Max Biofuel Blends'!F$11</f>
-        <v>9.9999999999980105E-3</v>
+        <v>-0.15999999999999659</v>
       </c>
       <c r="G7">
         <f>'Max Biofuel Blends'!G$11</f>
-        <v>1.9999999999996021E-2</v>
+        <v>-0.12000000000000455</v>
       </c>
       <c r="H7">
         <f>'Max Biofuel Blends'!H$11</f>
-        <v>2.9999999999997584E-2</v>
+        <v>-7.9999999999998295E-2</v>
       </c>
       <c r="I7">
         <f>'Max Biofuel Blends'!I$11</f>
-        <v>3.9999999999999147E-2</v>
+        <v>-3.9999999999992042E-2</v>
       </c>
       <c r="J7">
         <f>'Max Biofuel Blends'!J$11</f>
-        <v>4.9999999999997158E-2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <f>'Max Biofuel Blends'!K$11</f>
-        <v>5.9999999999998721E-2</v>
+        <v>4.0000000000006253E-2</v>
       </c>
       <c r="L7">
         <f>'Max Biofuel Blends'!L$11</f>
-        <v>6.9999999999996732E-2</v>
+        <v>7.9999999999998295E-2</v>
       </c>
       <c r="M7">
         <f>'Max Biofuel Blends'!M$11</f>
-        <v>7.9999999999998295E-2</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="N7">
         <f>'Max Biofuel Blends'!N$11</f>
-        <v>8.9999999999996305E-2</v>
+        <v>0.15999999999999659</v>
       </c>
       <c r="O7">
         <f>'Max Biofuel Blends'!O$11</f>
-        <v>9.9999999999997868E-2</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="P7">
         <f>'Max Biofuel Blends'!P$11</f>
-        <v>0.10999999999999943</v>
+        <v>0.24000000000000909</v>
       </c>
       <c r="Q7">
         <f>'Max Biofuel Blends'!Q$11</f>
-        <v>0.11999999999999744</v>
+        <v>0.28000000000000114</v>
       </c>
       <c r="R7">
         <f>'Max Biofuel Blends'!R$11</f>
-        <v>0.12999999999999901</v>
+        <v>0.32000000000000739</v>
       </c>
       <c r="S7">
         <f>'Max Biofuel Blends'!S$11</f>
-        <v>0.13999999999999702</v>
+        <v>0.35999999999999943</v>
       </c>
       <c r="T7">
         <f>'Max Biofuel Blends'!T$11</f>
-        <v>0.14999999999999858</v>
+        <v>0.40000000000000568</v>
       </c>
       <c r="U7">
         <f>'Max Biofuel Blends'!U$11</f>
-        <v>0.15999999999999659</v>
+        <v>0.43999999999999773</v>
       </c>
       <c r="V7">
         <f>'Max Biofuel Blends'!V$11</f>
-        <v>0.16999999999999815</v>
+        <v>0.48000000000000398</v>
       </c>
       <c r="W7">
         <f>'Max Biofuel Blends'!W$11</f>
-        <v>0.17999999999999616</v>
+        <v>0.51999999999999602</v>
       </c>
       <c r="X7">
         <f>'Max Biofuel Blends'!X$11</f>
-        <v>0.18999999999999773</v>
+        <v>0.56000000000000227</v>
       </c>
       <c r="Y7">
         <f>'Max Biofuel Blends'!Y$11</f>
-        <v>0.19999999999999929</v>
+        <v>0.60000000000000853</v>
       </c>
       <c r="Z7">
         <f>'Max Biofuel Blends'!Z$11</f>
-        <v>0.2099999999999973</v>
+        <v>0.64000000000000057</v>
       </c>
       <c r="AA7">
         <f>'Max Biofuel Blends'!AA$11</f>
-        <v>0.21999999999999886</v>
+        <v>0.68000000000000682</v>
       </c>
       <c r="AB7">
         <f>'Max Biofuel Blends'!AB$11</f>
-        <v>0.22999999999999687</v>
+        <v>0.71999999999999886</v>
       </c>
       <c r="AC7">
         <f>'Max Biofuel Blends'!AC$11</f>
-        <v>0.23999999999999844</v>
+        <v>0.76000000000000512</v>
       </c>
       <c r="AD7">
         <f>'Max Biofuel Blends'!AD$11</f>
-        <v>0.24999999999999645</v>
+        <v>0.79999999999999716</v>
       </c>
       <c r="AE7">
         <f>'Max Biofuel Blends'!AE$11</f>
-        <v>0.25999999999999801</v>
+        <v>0.84000000000000341</v>
       </c>
       <c r="AF7">
         <f>'Max Biofuel Blends'!AF$11</f>
-        <v>0.26999999999999602</v>
+        <v>0.87999999999999545</v>
       </c>
       <c r="AG7">
         <f>'Max Biofuel Blends'!AG$11</f>
-        <v>0.27999999999999758</v>
+        <v>0.92000000000000171</v>
       </c>
       <c r="AH7">
         <f>'Max Biofuel Blends'!AH$11</f>
-        <v>0.28999999999999915</v>
+        <v>0.96000000000000796</v>
       </c>
       <c r="AI7">
         <f>'Max Biofuel Blends'!AI$11</f>
-        <v>0.29999999999999716</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.2">
@@ -68385,143 +68385,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -74564,143 +74564,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
@@ -84527,143 +84527,143 @@
       </c>
       <c r="B7">
         <f t="shared" ref="B7:AJ7" si="0">max_biodsl</f>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="L7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="S7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="T7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="V7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="W7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="X7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AA7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AD7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AF7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AG7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AI7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="AJ7">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
